--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Ngày</t>
   </si>
@@ -48,6 +48,12 @@
   </si>
   <si>
     <t>Nghĩa</t>
+  </si>
+  <si>
+    <t>02/11/2025</t>
+  </si>
+  <si>
+    <t>Thử với hướng tiếp cận: dùng mô hình sentence transformers là paraphrase-multilingual-MiniLM-L12-v2, LLM là Qwen2-1.5B-Instruct, ChromaDB</t>
   </si>
 </sst>
 </file>
@@ -84,7 +90,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -107,37 +113,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -148,11 +128,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,11 +420,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="33.21875" defaultRowHeight="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="33.21875" style="1"/>
   </cols>
@@ -458,7 +444,7 @@
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -466,17 +452,61 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="4" spans="1:3" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
